--- a/numerical-workflows/v2/framework/经济/模块产销表/12_外循环_签到.xlsx
+++ b/numerical-workflows/v2/framework/经济/模块产销表/12_外循环_签到.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="产销阅读" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="资源汇总" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="机器明细" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阅读摘要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产销阅读" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源汇总" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="机器明细" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'产销阅读'!$A$1:$J$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资源汇总'!$A$1:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'资源汇总'!$A$1:$J$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'机器明细'!$A$1:$M$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -213,8 +213,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_resources" displayName="T_resources" ref="A1:J8" headerRowCount="1">
-  <autoFilter ref="A1:J8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_resources" displayName="T_resources" ref="A1:J13" headerRowCount="1">
+  <autoFilter ref="A1:J13"/>
   <tableColumns count="10">
     <tableColumn id="1" name="资源分类"/>
     <tableColumn id="2" name="资源/道具"/>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -664,7 +664,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>产出:3240.0</t>
+          <t>产出:1730.0</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>映射之匙(25) 合计x54；元能核心(105) 合计x29；随机史诗装备(2503) 合计x9；旅券(106) 合计x14；元晶(2) 合计x1650；随机传说装备(2504) 合计x4；熔晶(103) 合计x2</t>
+          <t>秘制炸鸡桶(105) 合计x29；元晶(2) 合计x1850；猎鹰金币(1) 合计x180000；旅券(106) 合计x14；房车零件(1074) 合计x500；未知笔记(110) 合计x10；映射之匙(25) 合计x8；熔晶(103) 合计x2；导能晶片(1154) 合计x2；稳固铆钉(1153) 合计x2；另2项</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>高敏感；周期/重复；随机/引用</t>
+          <t>高敏感；周期/重复</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：猎鹰金币(1) x20000</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>每日签到：随机史诗装备(2503) x1</t>
+          <t>每日签到：未知笔记(110) x2</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
@@ -961,7 +961,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：房车零件(1074) x100</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>每日签到：随机史诗装备(2503) x1</t>
+          <t>每日签到：猎鹰金币(1) x20000</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：映射之匙(25) x2</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：调校垫片(1152) x2</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>每日签到：随机传说装备(2504) x1</t>
+          <t>每日签到：元晶(2) x50</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：猎鹰金币(1) x20000</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>每日签到：随机史诗装备(2503) x1</t>
+          <t>每日签到：未知笔记(110) x2</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：房车零件(1074) x100</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>每日签到：随机史诗装备(2503) x1</t>
+          <t>每日签到：猎鹰金币(1) x20000</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：映射之匙(25) x2</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：稳固铆钉(1153) x2</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>每日签到：随机传说装备(2504) x1</t>
+          <t>每日签到：元晶(2) x50</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：猎鹰金币(1) x20000</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>每日签到：随机史诗装备(2503) x1</t>
+          <t>每日签到：未知笔记(110) x2</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：房车零件(1074) x100</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>每日签到：随机史诗装备(2503) x1</t>
+          <t>每日签到：猎鹰金币(1) x20000</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：映射之匙(25) x2</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：导能晶片(1154) x2</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>每日签到：随机传说装备(2504) x1</t>
+          <t>每日签到：元晶(2) x50</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：猎鹰金币(1) x20000</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>每日签到：随机史诗装备(2503) x1</t>
+          <t>每日签到：未知笔记(110) x2</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：房车零件(1074) x100</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>每日签到：随机史诗装备(2503) x1</t>
+          <t>每日签到：猎鹰金币(1) x20000</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：映射之匙(25) x2</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：精修胶带(1155) x2</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>每日签到：随机传说装备(2504) x1</t>
+          <t>每日签到：元晶(2) x50</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr"/>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：猎鹰金币(1) x20000</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>每日签到：随机史诗装备(2503) x1</t>
+          <t>每日签到：未知笔记(110) x2</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>每日签到：映射之匙(25) x3</t>
+          <t>每日签到：房车零件(1074) x100</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>累计签到：元晶(2) x100；累计签到：元能核心(105) x1</t>
+          <t>累计签到：元晶(2) x100；累计签到：秘制炸鸡桶(105) x1</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr"/>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>累计签到：元能核心(105) x1；累计签到：旅券(106) x2</t>
+          <t>累计签到：旅券(106) x2；累计签到：秘制炸鸡桶(105) x1</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>累计签到：元晶(2) x400；累计签到：元能核心(105) x2</t>
+          <t>累计签到：元晶(2) x400；累计签到：秘制炸鸡桶(105) x2</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>累计签到：元能核心(105) x2；累计签到：熔晶(103) x1</t>
+          <t>累计签到：熔晶(103) x1；累计签到：秘制炸鸡桶(105) x2</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>累计签到：元能核心(105) x2；累计签到：旅券(106) x2</t>
+          <t>累计签到：旅券(106) x2；累计签到：秘制炸鸡桶(105) x2</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>累计签到：元晶(2) x1000；累计签到：元能核心(105) x3</t>
+          <t>累计签到：元晶(2) x1000；累计签到：秘制炸鸡桶(105) x3</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>累计签到：元能核心(105) x3；累计签到：熔晶(103) x1</t>
+          <t>累计签到：熔晶(103) x1；累计签到：秘制炸鸡桶(105) x3</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>累计签到：元能核心(105) x5；累计签到：旅券(106) x3</t>
+          <t>累计签到：旅券(106) x3；累计签到：秘制炸鸡桶(105) x5</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>累计签到：元能核心(105) x5；累计签到：旅券(106) x3</t>
+          <t>累计签到：旅券(106) x3；累计签到：秘制炸鸡桶(105) x5</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>累计签到：元能核心(105) x5；累计签到：旅券(106) x3</t>
+          <t>累计签到：旅券(106) x3；累计签到：秘制炸鸡桶(105) x5</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>元能核心</t>
+          <t>秘制炸鸡桶</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>熔晶</t>
+          <t>房车零件</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
@@ -2940,48 +2940,48 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>累计签到 x2</t>
+          <t>每日签到 x5</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>签到 x2</t>
+          <t>签到 x5</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>常规</t>
+          <t>周期/重复</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>养成材料</t>
+          <t>其他资源</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>未知笔记</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -2990,26 +2990,26 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>每日签到 x18</t>
+          <t>每日签到 x5</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>签到 x18</t>
+          <t>签到 x5</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -3021,17 +3021,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>养成材料</t>
+          <t>其他资源</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>随机史诗装备</t>
+          <t>熔晶</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -3040,11 +3040,11 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -3054,34 +3054,34 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>每日签到 x9</t>
+          <t>累计签到 x2</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>签到 x9</t>
+          <t>签到 x2</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>周期/重复；随机/引用</t>
+          <t>常规</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>养成材料</t>
+          <t>其他资源</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>随机传说装备</t>
+          <t>导能晶片</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -3090,11 +3090,11 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -3104,49 +3104,49 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>每日签到 x4</t>
+          <t>每日签到</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>签到 x4</t>
+          <t>签到</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>周期/重复；随机/引用</t>
+          <t>周期/重复</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>基础货币/体力</t>
+          <t>其他资源</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>稳固铆钉</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
+          <t>1153</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>产出</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
           <t>0</t>
@@ -3154,72 +3154,322 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>累计签到 x5</t>
+          <t>每日签到</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>签到 x5</t>
+          <t>签到</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>高敏感</t>
+          <t>周期/重复</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>其他资源</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>精修胶带</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>每日签到</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>签到</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>周期/重复</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>其他资源</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>调校垫片</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>1152</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>每日签到</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>签到</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>周期/重复</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>养成材料</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>映射之匙</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>每日签到 x4</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>签到 x4</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>周期/重复</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>基础货币/体力</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>元晶</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>累计签到 x5；每日签到 x4</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>签到 x9</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>高敏感；周期/重复</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>基础货币/体力</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>猎鹰金币</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>每日签到 x9</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>签到 x9</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>周期/重复</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
           <t>抽卡/角色获取</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>旅券</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>产出</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n">
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>产出</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>累计签到 x6</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>签到 x6</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>常规</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J8"/>
+  <autoFilter ref="A1:J13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3331,15 +3581,13 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>猎鹰金币</t>
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>180</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="inlineStr"/>
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr">
@@ -3384,11 +3632,11 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>随机史诗装备</t>
+          <t>未知笔记</t>
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr"/>
@@ -3435,14 +3683,14 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>房车零件</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr"/>
@@ -3488,11 +3736,11 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>随机史诗装备</t>
+          <t>猎鹰金币</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1</v>
+        <v>20000</v>
       </c>
       <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="5" t="inlineStr"/>
@@ -3543,10 +3791,10 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
@@ -3592,15 +3840,13 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>调校垫片</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>180</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr">
@@ -3645,11 +3891,11 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>随机传说装备</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E8" s="5" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr"/>
@@ -3696,15 +3942,13 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>猎鹰金币</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>180</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr">
@@ -3749,11 +3993,11 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>随机史诗装备</t>
+          <t>未知笔记</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr"/>
       <c r="F10" s="5" t="inlineStr"/>
@@ -3800,14 +4044,14 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>房车零件</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="inlineStr"/>
@@ -3853,11 +4097,11 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>随机史诗装备</t>
+          <t>猎鹰金币</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1</v>
+        <v>20000</v>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="5" t="inlineStr"/>
@@ -3908,10 +4152,10 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr"/>
@@ -3957,15 +4201,13 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>稳固铆钉</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>180</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr">
@@ -4010,11 +4252,11 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>随机传说装备</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E15" s="5" t="inlineStr"/>
       <c r="F15" s="5" t="inlineStr"/>
@@ -4061,15 +4303,13 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>猎鹰金币</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>180</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr">
@@ -4114,11 +4354,11 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>随机史诗装备</t>
+          <t>未知笔记</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr"/>
       <c r="F17" s="5" t="inlineStr"/>
@@ -4165,14 +4405,14 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>房车零件</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr"/>
@@ -4218,11 +4458,11 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>随机史诗装备</t>
+          <t>猎鹰金币</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>20000</v>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="5" t="inlineStr"/>
@@ -4273,10 +4513,10 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr"/>
@@ -4322,15 +4562,13 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>导能晶片</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>180</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="5" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr">
@@ -4375,11 +4613,11 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>随机传说装备</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
       <c r="F22" s="5" t="inlineStr"/>
@@ -4426,15 +4664,13 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>猎鹰金币</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>180</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="5" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr">
@@ -4479,11 +4715,11 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>随机史诗装备</t>
+          <t>未知笔记</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="5" t="inlineStr"/>
@@ -4530,14 +4766,14 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>房车零件</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="inlineStr"/>
@@ -4583,11 +4819,11 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>随机史诗装备</t>
+          <t>猎鹰金币</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>1</v>
+        <v>20000</v>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr"/>
@@ -4638,10 +4874,10 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
       <c r="G27" s="5" t="inlineStr"/>
@@ -4687,15 +4923,13 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>精修胶带</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>180</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr">
@@ -4740,11 +4974,11 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>随机传说装备</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="5" t="inlineStr"/>
@@ -4791,15 +5025,13 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>猎鹰金币</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>180</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr">
@@ -4844,11 +5076,11 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>随机史诗装备</t>
+          <t>未知笔记</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr"/>
@@ -4895,14 +5127,14 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>映射之匙</t>
+          <t>房车零件</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr"/>
@@ -4999,7 +5231,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>元能核心</t>
+          <t>秘制炸鸡桶</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
@@ -5050,11 +5282,11 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>元能核心</t>
+          <t>旅券</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="inlineStr"/>
       <c r="F35" s="5" t="inlineStr"/>
@@ -5101,11 +5333,11 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>旅券</t>
+          <t>秘制炸鸡桶</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="5" t="inlineStr"/>
@@ -5254,7 +5486,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>元能核心</t>
+          <t>秘制炸鸡桶</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
@@ -5356,11 +5588,11 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>元能核心</t>
+          <t>熔晶</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="5" t="inlineStr"/>
@@ -5407,11 +5639,11 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>熔晶</t>
+          <t>秘制炸鸡桶</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="5" t="inlineStr"/>
@@ -5509,7 +5741,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>元能核心</t>
+          <t>旅券</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
@@ -5560,7 +5792,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>旅券</t>
+          <t>秘制炸鸡桶</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
@@ -5662,7 +5894,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>元能核心</t>
+          <t>秘制炸鸡桶</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
@@ -5713,11 +5945,11 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>元能核心</t>
+          <t>熔晶</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="5" t="inlineStr"/>
@@ -5764,11 +5996,11 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>熔晶</t>
+          <t>秘制炸鸡桶</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E49" s="5" t="inlineStr"/>
       <c r="F49" s="5" t="inlineStr"/>
@@ -5815,11 +6047,11 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>元能核心</t>
+          <t>旅券</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E50" s="5" t="inlineStr"/>
       <c r="F50" s="5" t="inlineStr"/>
@@ -5866,11 +6098,11 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>旅券</t>
+          <t>秘制炸鸡桶</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E51" s="5" t="inlineStr"/>
       <c r="F51" s="5" t="inlineStr"/>
@@ -5917,11 +6149,11 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>元能核心</t>
+          <t>旅券</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E52" s="5" t="inlineStr"/>
       <c r="F52" s="5" t="inlineStr"/>
@@ -5968,11 +6200,11 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>旅券</t>
+          <t>秘制炸鸡桶</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E53" s="5" t="inlineStr"/>
       <c r="F53" s="5" t="inlineStr"/>
@@ -6019,11 +6251,11 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>元能核心</t>
+          <t>旅券</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="5" t="inlineStr"/>
@@ -6070,11 +6302,11 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>旅券</t>
+          <t>秘制炸鸡桶</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E55" s="5" t="inlineStr"/>
       <c r="F55" s="5" t="inlineStr"/>
